--- a/data/trans_dic/P1409-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1409-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,06</t>
+          <t>1,13; 4,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,72</t>
+          <t>1,6; 6,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,76</t>
+          <t>1,7; 6,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,42</t>
+          <t>1,85; 6,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,44</t>
+          <t>1,96; 6,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,28</t>
+          <t>2,39; 5,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,14</t>
+          <t>2,01; 5,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,42</t>
+          <t>2,21; 5,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,9</t>
+          <t>2,37; 5,38</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,42</t>
+          <t>0,58; 2,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,53</t>
+          <t>0,42; 2,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,05</t>
+          <t>2,64; 7,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,57</t>
+          <t>2,01; 5,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,44</t>
+          <t>2,1; 5,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,22</t>
+          <t>3,1; 6,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,51</t>
+          <t>1,6; 3,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,45</t>
+          <t>1,57; 3,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,27</t>
+          <t>3,4; 6,02</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,73</t>
+          <t>0,63; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,14</t>
+          <t>0,63; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,64</t>
+          <t>2,91; 7,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,59</t>
+          <t>0,87; 4,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,17</t>
+          <t>1,94; 6,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,42</t>
+          <t>3,31; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,21</t>
+          <t>1,06; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,45</t>
+          <t>1,63; 4,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,36</t>
+          <t>3,35; 6,17</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,79; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,65</t>
+          <t>2,14; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,32</t>
+          <t>1,65; 8,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,19</t>
+          <t>1,03; 4,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,85</t>
+          <t>3,24; 7,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 47,9</t>
+          <t>1,04; 3,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,28</t>
+          <t>1,19; 3,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,38</t>
+          <t>3,32; 6,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 34,35</t>
+          <t>1,63; 4,73</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,47</t>
+          <t>0,92; 5,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,34</t>
+          <t>0,92; 5,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,13</t>
+          <t>0,47; 4,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,01</t>
+          <t>0,95; 6,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,05</t>
+          <t>1,27; 6,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,21</t>
+          <t>2,77; 7,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,28</t>
+          <t>1,33; 4,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,44</t>
+          <t>1,55; 4,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,65</t>
+          <t>1,97; 5,05</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,92</t>
+          <t>1,11; 4,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,3</t>
+          <t>0,32; 3,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,89</t>
+          <t>2,11; 5,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,69</t>
+          <t>1,43; 5,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,85</t>
+          <t>1,4; 5,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,82</t>
+          <t>3,52; 7,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,71</t>
+          <t>1,67; 4,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,71</t>
+          <t>1,1; 3,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,18</t>
+          <t>3,29; 6,04</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,83</t>
+          <t>0,72; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,97</t>
+          <t>1,93; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,56</t>
+          <t>2,36; 6,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,69</t>
+          <t>1,25; 3,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,29</t>
+          <t>3,06; 6,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,25</t>
+          <t>6,3; 9,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,8</t>
+          <t>1,12; 2,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,05</t>
+          <t>2,8; 5,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,58</t>
+          <t>4,84; 7,55</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,47</t>
+          <t>1,21; 3,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,58</t>
+          <t>1,51; 3,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,88</t>
+          <t>2,76; 5,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,08</t>
+          <t>1,63; 3,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,07</t>
+          <t>2,86; 5,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,01</t>
+          <t>2,74; 4,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,29</t>
+          <t>1,69; 3,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,42</t>
+          <t>2,46; 4,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,33</t>
+          <t>2,97; 4,89</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,48</t>
+          <t>1,48; 2,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,13</t>
+          <t>2,02; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,61</t>
+          <t>3,16; 4,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,37</t>
+          <t>2,19; 3,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,69</t>
+          <t>3,38; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,9</t>
+          <t>4,25; 5,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,73</t>
+          <t>2,0; 2,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,75</t>
+          <t>2,86; 3,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,73</t>
+          <t>3,88; 4,82</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>22618</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3706; 14909</t>
+          <t>3320; 14516</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5556; 19743</t>
+          <t>4705; 18391</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5973; 30394</t>
+          <t>5407; 21360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5877; 21323</t>
+          <t>5328; 19272</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5571; 18582</t>
+          <t>5657; 18333</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7547; 18189</t>
+          <t>7547; 17881</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12013; 29918</t>
+          <t>11704; 29637</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12622; 31553</t>
+          <t>12878; 32087</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16498; 41454</t>
+          <t>15036; 34173</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>48751</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2099; 12251</t>
+          <t>2916; 13247</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1846; 12719</t>
+          <t>2126; 12724</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13397; 41654</t>
+          <t>13967; 40640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10799; 29167</t>
+          <t>10519; 28573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11290; 28436</t>
+          <t>11002; 27662</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16631; 31915</t>
+          <t>16888; 33124</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15605; 36128</t>
+          <t>16430; 36272</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15270; 35380</t>
+          <t>16095; 35951</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33860; 64574</t>
+          <t>36480; 64657</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31679</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2033; 12082</t>
+          <t>2034; 12532</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2497; 13201</t>
+          <t>2019; 13784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7933; 20983</t>
+          <t>9192; 22508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2970; 15664</t>
+          <t>2975; 15516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6135; 20750</t>
+          <t>6516; 21771</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11610; 25910</t>
+          <t>11787; 25208</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6988; 21316</t>
+          <t>7030; 23066</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10548; 29173</t>
+          <t>10681; 29942</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23090; 42305</t>
+          <t>22514; 41503</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76523</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>20800</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3235; 14315</t>
+          <t>2941; 13464</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8475; 24588</t>
+          <t>7930; 23541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5900; 29131</t>
+          <t>6145; 31936</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3950; 16314</t>
+          <t>3987; 15615</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12344; 30402</t>
+          <t>12529; 29955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6228; 227878</t>
+          <t>4396; 14233</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10102; 25046</t>
+          <t>9107; 25140</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25279; 48330</t>
+          <t>25109; 49873</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17353; 270810</t>
+          <t>12947; 37611</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13616</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1954; 11638</t>
+          <t>1950; 12504</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1974; 11275</t>
+          <t>1948; 10993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>838; 9165</t>
+          <t>970; 9576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1928; 13204</t>
+          <t>2090; 13191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2980; 13223</t>
+          <t>2769; 13227</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6640; 19114</t>
+          <t>6248; 17010</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4925; 18518</t>
+          <t>5765; 18978</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6374; 19087</t>
+          <t>6670; 21220</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8346; 21818</t>
+          <t>8523; 21812</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>23782</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3016; 13483</t>
+          <t>3029; 13393</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>833; 8688</t>
+          <t>834; 8085</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5554; 15872</t>
+          <t>5721; 15677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4018; 15825</t>
+          <t>3989; 16464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3887; 15989</t>
+          <t>3830; 15055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9372; 20061</t>
+          <t>9263; 20408</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9906; 25995</t>
+          <t>9194; 25033</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6413; 19907</t>
+          <t>5913; 19587</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17516; 32516</t>
+          <t>17585; 32265</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>89069</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4834; 18751</t>
+          <t>4759; 18529</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12820; 32634</t>
+          <t>12686; 30759</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13656; 40748</t>
+          <t>16912; 47390</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7908; 25636</t>
+          <t>8673; 27486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20508; 43500</t>
+          <t>21167; 42886</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24111; 70040</t>
+          <t>48548; 75381</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15927; 37928</t>
+          <t>15261; 36653</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38411; 68005</t>
+          <t>37727; 67867</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46650; 96674</t>
+          <t>72050; 112254</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>32354</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>63263</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9331; 27041</t>
+          <t>9390; 26777</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11823; 27864</t>
+          <t>11737; 27804</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12118; 45326</t>
+          <t>22042; 47381</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13830; 33501</t>
+          <t>13416; 32169</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24296; 50150</t>
+          <t>23617; 48637</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19133; 35859</t>
+          <t>22734; 40391</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27658; 52721</t>
+          <t>27011; 51531</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>38794; 70896</t>
+          <t>39469; 68574</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33713; 71120</t>
+          <t>48303; 79630</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51408; 84834</t>
+          <t>50578; 83690</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>68851; 106386</t>
+          <t>68484; 106829</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95309; 159198</t>
+          <t>111411; 165220</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78185; 119660</t>
+          <t>77982; 119290</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>119238; 166235</t>
+          <t>119676; 166461</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>152418; 508248</t>
+          <t>158583; 200886</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>139010; 190369</t>
+          <t>139304; 190443</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>200126; 260204</t>
+          <t>198200; 259201</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>273464; 620534</t>
+          <t>281706; 349650</t>
         </is>
       </c>
     </row>
